--- a/output/roomself_excel/10441.xlsx
+++ b/output/roomself_excel/10441.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>405305</v>
+        <v>108675</v>
       </c>
       <c r="D2" t="n">
-        <v>9380</v>
+        <v>2832</v>
       </c>
       <c r="E2" t="n">
-        <v>1014</v>
+        <v>506</v>
       </c>
       <c r="F2" t="n">
-        <v>621</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93624</v>
+        <v>156219</v>
       </c>
       <c r="D3" t="n">
-        <v>2500</v>
+        <v>4001</v>
       </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="F3" t="n">
-        <v>270</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>139616</v>
+        <v>93624</v>
       </c>
       <c r="D4" t="n">
-        <v>3088</v>
+        <v>2500</v>
       </c>
       <c r="E4" t="n">
-        <v>643</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>464</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>161207</v>
+        <v>139616</v>
       </c>
       <c r="D5" t="n">
-        <v>4344</v>
+        <v>3088</v>
       </c>
       <c r="E5" t="n">
-        <v>1014</v>
+        <v>464</v>
       </c>
       <c r="F5" t="n">
-        <v>643</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>2576</v>
       </c>
       <c r="E6" t="n">
-        <v>621</v>
+        <v>361</v>
       </c>
       <c r="F6" t="n">
-        <v>361</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33401</v>
+        <v>16758</v>
       </c>
       <c r="D7" t="n">
-        <v>1560</v>
+        <v>1036</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16758</v>
+        <v>21190</v>
       </c>
       <c r="D8" t="n">
-        <v>1036</v>
+        <v>1172</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21190</v>
+        <v>65436</v>
       </c>
       <c r="D9" t="n">
-        <v>1172</v>
+        <v>2252</v>
       </c>
       <c r="E9" t="n">
+        <v>425</v>
+      </c>
+      <c r="F9" t="n">
         <v>188</v>
-      </c>
-      <c r="F9" t="n">
-        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17115</v>
+        <v>161207</v>
       </c>
       <c r="D10" t="n">
-        <v>1072</v>
+        <v>4344</v>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>642</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30504</v>
+        <v>140411</v>
       </c>
       <c r="D11" t="n">
-        <v>1400</v>
+        <v>5024</v>
       </c>
       <c r="E11" t="n">
-        <v>207</v>
+        <v>308</v>
       </c>
       <c r="F11" t="n">
-        <v>188</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -686,19 +686,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65436</v>
+        <v>17115</v>
       </c>
       <c r="D12" t="n">
-        <v>2252</v>
+        <v>1072</v>
       </c>
       <c r="E12" t="n">
-        <v>425</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>33401</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E13" t="n">
+        <v>127</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>30504</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E14" t="n">
+        <v>207</v>
+      </c>
+      <c r="F14" t="n">
         <v>188</v>
       </c>
     </row>

--- a/output/roomself_excel/10441.xlsx
+++ b/output/roomself_excel/10441.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2832</v>
       </c>
-      <c r="E2" t="n">
-        <v>506</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>253</v>
+        <v>225</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>483</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>4001</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>368</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>432</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2500</v>
       </c>
-      <c r="E4" t="n">
-        <v>400</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>270</v>
+        <v>249</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>376</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>3088</v>
       </c>
-      <c r="E5" t="n">
-        <v>464</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>358</v>
+        <v>332</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>440</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +647,27 @@
       <c r="D6" t="n">
         <v>2576</v>
       </c>
-      <c r="E6" t="n">
-        <v>361</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>330</v>
+        <v>314</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>331</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +685,20 @@
       <c r="D7" t="n">
         <v>1036</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>126</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>21</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +715,27 @@
       <c r="D8" t="n">
         <v>1172</v>
       </c>
-      <c r="E8" t="n">
-        <v>188</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>158</v>
+        <v>163</v>
+      </c>
+      <c r="G8" t="n">
+        <v>28</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>119</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +753,27 @@
       <c r="D9" t="n">
         <v>2252</v>
       </c>
-      <c r="E9" t="n">
-        <v>425</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>188</v>
+        <v>164</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>399</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +791,27 @@
       <c r="D10" t="n">
         <v>4344</v>
       </c>
-      <c r="E10" t="n">
-        <v>642</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>258</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>196</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +829,27 @@
       <c r="D11" t="n">
         <v>5024</v>
       </c>
-      <c r="E11" t="n">
-        <v>308</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>97</v>
+        <v>192</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>218</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +867,20 @@
       <c r="D12" t="n">
         <v>1072</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>105</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>25</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +897,20 @@
       <c r="D13" t="n">
         <v>1560</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>127</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>26</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +927,27 @@
       <c r="D14" t="n">
         <v>1400</v>
       </c>
-      <c r="E14" t="n">
-        <v>207</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>188</v>
+        <v>164</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>186</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
